--- a/data/dividends_info_20260726.xlsx
+++ b/data/dividends_info_20260726.xlsx
@@ -3774,7 +3774,7 @@
     <row r="91">
       <c r="A91" t="inlineStr">
         <is>
-          <t>FinecoBank S.p.A.</t>
+          <t>AMPLIFON S.p.A.</t>
         </is>
       </c>
       <c r="B91" t="inlineStr">
@@ -3791,7 +3791,7 @@
     <row r="92">
       <c r="A92" t="inlineStr">
         <is>
-          <t>A2A S.p.A.</t>
+          <t>AMPLIFON S.p.A.</t>
         </is>
       </c>
       <c r="B92" t="inlineStr">
@@ -3808,7 +3808,7 @@
     <row r="93">
       <c r="A93" t="inlineStr">
         <is>
-          <t>AEDES S.p.A.</t>
+          <t>ARNOLDO MONDADORI EDITORE S.p.A.</t>
         </is>
       </c>
       <c r="B93" t="inlineStr">
@@ -3825,7 +3825,7 @@
     <row r="94">
       <c r="A94" t="inlineStr">
         <is>
-          <t>AMPLIFON S.p.A.</t>
+          <t>ARNOLDO MONDADORI EDITORE S.p.A.</t>
         </is>
       </c>
       <c r="B94" t="inlineStr">
@@ -3842,7 +3842,7 @@
     <row r="95">
       <c r="A95" t="inlineStr">
         <is>
-          <t>AMPLIFON S.p.A.</t>
+          <t>ASCOPIAVE S.p.A.</t>
         </is>
       </c>
       <c r="B95" t="inlineStr">
@@ -3859,7 +3859,7 @@
     <row r="96">
       <c r="A96" t="inlineStr">
         <is>
-          <t>ARNOLDO MONDADORI EDITORE S.p.A.</t>
+          <t>AEDES S.p.A.</t>
         </is>
       </c>
       <c r="B96" t="inlineStr">
@@ -3876,7 +3876,7 @@
     <row r="97">
       <c r="A97" t="inlineStr">
         <is>
-          <t>ARNOLDO MONDADORI EDITORE S.p.A.</t>
+          <t>ASCOPIAVE S.p.A.</t>
         </is>
       </c>
       <c r="B97" t="inlineStr">
@@ -3893,7 +3893,7 @@
     <row r="98">
       <c r="A98" t="inlineStr">
         <is>
-          <t>ASCOPIAVE S.p.A.</t>
+          <t>AZIMUT HOLDING S.p.A.</t>
         </is>
       </c>
       <c r="B98" t="inlineStr">
@@ -3910,7 +3910,7 @@
     <row r="99">
       <c r="A99" t="inlineStr">
         <is>
-          <t>AZIMUT HOLDING S.p.A.</t>
+          <t>Alerion Clean Power S.p.A.</t>
         </is>
       </c>
       <c r="B99" t="inlineStr">
@@ -3927,7 +3927,7 @@
     <row r="100">
       <c r="A100" t="inlineStr">
         <is>
-          <t>Alerion Clean Power S.p.A.</t>
+          <t>BANCA MEDIOLANUM S.p.A.</t>
         </is>
       </c>
       <c r="B100" t="inlineStr">
@@ -3944,7 +3944,7 @@
     <row r="101">
       <c r="A101" t="inlineStr">
         <is>
-          <t>BANCA MEDIOLANUM S.p.A.</t>
+          <t>BANCO DI DESIO E DELLA BRIANZA S.p.A.</t>
         </is>
       </c>
       <c r="B101" t="inlineStr">
@@ -3961,7 +3961,7 @@
     <row r="102">
       <c r="A102" t="inlineStr">
         <is>
-          <t>BANCO DI DESIO E DELLA BRIANZA S.p.A.</t>
+          <t>BRUNELLO CUCINELLI S.p.A.</t>
         </is>
       </c>
       <c r="B102" t="inlineStr">
@@ -3988,14 +3988,14 @@
       </c>
       <c r="C103" t="inlineStr">
         <is>
-          <t>Half Year Report</t>
+          <t>Analyst Presentation</t>
         </is>
       </c>
     </row>
     <row r="104">
       <c r="A104" t="inlineStr">
         <is>
-          <t>BRUNELLO CUCINELLI S.p.A.</t>
+          <t>A2A S.p.A.</t>
         </is>
       </c>
       <c r="B104" t="inlineStr">
@@ -4005,14 +4005,14 @@
       </c>
       <c r="C104" t="inlineStr">
         <is>
-          <t>Analyst Presentation</t>
+          <t>Half Year Report</t>
         </is>
       </c>
     </row>
     <row r="105">
       <c r="A105" t="inlineStr">
         <is>
-          <t>ASCOPIAVE S.p.A.</t>
+          <t>CALTAGIRONE S.p.A.</t>
         </is>
       </c>
       <c r="B105" t="inlineStr">
@@ -4022,14 +4022,14 @@
       </c>
       <c r="C105" t="inlineStr">
         <is>
-          <t>Analyst Presentation</t>
+          <t>Half Year Report</t>
         </is>
       </c>
     </row>
     <row r="106">
       <c r="A106" t="inlineStr">
         <is>
-          <t>CALTAGIRONE S.p.A.</t>
+          <t>Banca Profilo S.p.A.</t>
         </is>
       </c>
       <c r="B106" t="inlineStr">
@@ -4046,7 +4046,7 @@
     <row r="107">
       <c r="A107" t="inlineStr">
         <is>
-          <t>Banca Profilo S.p.A.</t>
+          <t>ELICA S.p.A.</t>
         </is>
       </c>
       <c r="B107" t="inlineStr">
@@ -4063,7 +4063,7 @@
     <row r="108">
       <c r="A108" t="inlineStr">
         <is>
-          <t>ESAUTOMOTION S.p.A.</t>
+          <t>ENEL S.p.A.</t>
         </is>
       </c>
       <c r="B108" t="inlineStr">
@@ -4073,7 +4073,7 @@
       </c>
       <c r="C108" t="inlineStr">
         <is>
-          <t>Half Year Preliminary Results</t>
+          <t>Analyst Presentation</t>
         </is>
       </c>
     </row>
@@ -4097,7 +4097,7 @@
     <row r="110">
       <c r="A110" t="inlineStr">
         <is>
-          <t>ENEL S.p.A.</t>
+          <t>ESAUTOMOTION S.p.A.</t>
         </is>
       </c>
       <c r="B110" t="inlineStr">
@@ -4107,14 +4107,14 @@
       </c>
       <c r="C110" t="inlineStr">
         <is>
-          <t>Analyst Presentation</t>
+          <t>Half Year Preliminary Results</t>
         </is>
       </c>
     </row>
     <row r="111">
       <c r="A111" t="inlineStr">
         <is>
-          <t>ELICA S.p.A.</t>
+          <t>Ferrari N.V.</t>
         </is>
       </c>
       <c r="B111" t="inlineStr">
@@ -4124,14 +4124,14 @@
       </c>
       <c r="C111" t="inlineStr">
         <is>
-          <t>Half Year Report</t>
+          <t>Analyst Presentation</t>
         </is>
       </c>
     </row>
     <row r="112">
       <c r="A112" t="inlineStr">
         <is>
-          <t>DE' LONGHI S.p.A.</t>
+          <t>DEA CAPITAL REAL ESTATE SGR S.p.A.</t>
         </is>
       </c>
       <c r="B112" t="inlineStr">
@@ -4148,7 +4148,7 @@
     <row r="113">
       <c r="A113" t="inlineStr">
         <is>
-          <t>DEA CAPITAL REAL ESTATE SGR S.p.A.</t>
+          <t>DE' LONGHI S.p.A.</t>
         </is>
       </c>
       <c r="B113" t="inlineStr">
@@ -4158,14 +4158,14 @@
       </c>
       <c r="C113" t="inlineStr">
         <is>
-          <t>Half Year Report</t>
+          <t>Analyst Presentation</t>
         </is>
       </c>
     </row>
     <row r="114">
       <c r="A114" t="inlineStr">
         <is>
-          <t>Ferrari N.V.</t>
+          <t>D'AMICO INTERNATIONAL SHIPPING S.A.</t>
         </is>
       </c>
       <c r="B114" t="inlineStr">
@@ -4175,7 +4175,7 @@
       </c>
       <c r="C114" t="inlineStr">
         <is>
-          <t>Analyst Presentation</t>
+          <t>Half Year Report</t>
         </is>
       </c>
     </row>
@@ -4192,14 +4192,14 @@
       </c>
       <c r="C115" t="inlineStr">
         <is>
-          <t>Half Year Report</t>
+          <t>Analyst Presentation</t>
         </is>
       </c>
     </row>
     <row r="116">
       <c r="A116" t="inlineStr">
         <is>
-          <t>D'AMICO INTERNATIONAL SHIPPING S.A.</t>
+          <t>FinecoBank S.p.A.</t>
         </is>
       </c>
       <c r="B116" t="inlineStr">
@@ -4243,7 +4243,7 @@
       </c>
       <c r="C118" t="inlineStr">
         <is>
-          <t>Analyst Presentation</t>
+          <t>Half Year Report</t>
         </is>
       </c>
     </row>
@@ -4260,14 +4260,14 @@
       </c>
       <c r="C119" t="inlineStr">
         <is>
-          <t>Analyst Presentation</t>
+          <t>Half Year Report</t>
         </is>
       </c>
     </row>
     <row r="120">
       <c r="A120" t="inlineStr">
         <is>
-          <t>CONVERGENZE S.p.A. SOCIETA' BENEFIT</t>
+          <t>Misitano &amp; Stracuzzi S.p.A.</t>
         </is>
       </c>
       <c r="B120" t="inlineStr">
@@ -4277,14 +4277,14 @@
       </c>
       <c r="C120" t="inlineStr">
         <is>
-          <t>Half Year Preliminary Results</t>
+          <t>Annual General Meeting</t>
         </is>
       </c>
     </row>
     <row r="121">
       <c r="A121" t="inlineStr">
         <is>
-          <t>DiaSorin S.p.A</t>
+          <t>GREEN OLEO S.p.A</t>
         </is>
       </c>
       <c r="B121" t="inlineStr">
@@ -4294,14 +4294,14 @@
       </c>
       <c r="C121" t="inlineStr">
         <is>
-          <t>Half Year Report</t>
+          <t>Half Year Preliminary Results</t>
         </is>
       </c>
     </row>
     <row r="122">
       <c r="A122" t="inlineStr">
         <is>
-          <t>ERG S.p.A.</t>
+          <t>Ferretti S.p.A.</t>
         </is>
       </c>
       <c r="B122" t="inlineStr">
@@ -4318,7 +4318,7 @@
     <row r="123">
       <c r="A123" t="inlineStr">
         <is>
-          <t>Ferretti S.p.A.</t>
+          <t>ERG S.p.A.</t>
         </is>
       </c>
       <c r="B123" t="inlineStr">
@@ -4328,14 +4328,14 @@
       </c>
       <c r="C123" t="inlineStr">
         <is>
-          <t>Half Year Report</t>
+          <t>Analyst Presentation</t>
         </is>
       </c>
     </row>
     <row r="124">
       <c r="A124" t="inlineStr">
         <is>
-          <t>Tinexta S.p.A.</t>
+          <t>DiaSorin S.p.A</t>
         </is>
       </c>
       <c r="B124" t="inlineStr">
@@ -4345,14 +4345,14 @@
       </c>
       <c r="C124" t="inlineStr">
         <is>
-          <t>Analyst Presentation</t>
+          <t>Half Year Report</t>
         </is>
       </c>
     </row>
     <row r="125">
       <c r="A125" t="inlineStr">
         <is>
-          <t>Misitano &amp; Stracuzzi S.p.A.</t>
+          <t>BIESSE S.p.A.</t>
         </is>
       </c>
       <c r="B125" t="inlineStr">
@@ -4362,14 +4362,14 @@
       </c>
       <c r="C125" t="inlineStr">
         <is>
-          <t>Annual General Meeting</t>
+          <t>Half Year Report</t>
         </is>
       </c>
     </row>
     <row r="126">
       <c r="A126" t="inlineStr">
         <is>
-          <t>Nusco S.p.A.</t>
+          <t>CONVERGENZE S.p.A. SOCIETA' BENEFIT</t>
         </is>
       </c>
       <c r="B126" t="inlineStr">
@@ -4386,7 +4386,7 @@
     <row r="127">
       <c r="A127" t="inlineStr">
         <is>
-          <t>Svas Biosana S.p.A.</t>
+          <t>CIR S.p.A. - COMPAGNIE INDUSTRIALI RIUNITE</t>
         </is>
       </c>
       <c r="B127" t="inlineStr">
@@ -4396,14 +4396,14 @@
       </c>
       <c r="C127" t="inlineStr">
         <is>
-          <t>Half Year Preliminary Results</t>
+          <t>Half Year Report</t>
         </is>
       </c>
     </row>
     <row r="128">
       <c r="A128" t="inlineStr">
         <is>
-          <t>The Italian Sea Group S.p.A.</t>
+          <t>CAIRO COMMUNICATION S.p.A.</t>
         </is>
       </c>
       <c r="B128" t="inlineStr">
@@ -4413,14 +4413,14 @@
       </c>
       <c r="C128" t="inlineStr">
         <is>
-          <t>Bod Annual Report</t>
+          <t>Half Year Report</t>
         </is>
       </c>
     </row>
     <row r="129">
       <c r="A129" t="inlineStr">
         <is>
-          <t>CIR S.p.A. - COMPAGNIE INDUSTRIALI RIUNITE</t>
+          <t>Basic Net S.p.A.</t>
         </is>
       </c>
       <c r="B129" t="inlineStr">
@@ -4430,14 +4430,14 @@
       </c>
       <c r="C129" t="inlineStr">
         <is>
-          <t>Half Year Report</t>
+          <t>Analyst Presentation</t>
         </is>
       </c>
     </row>
     <row r="130">
       <c r="A130" t="inlineStr">
         <is>
-          <t>VNE S.p.A.</t>
+          <t>Basic Net S.p.A.</t>
         </is>
       </c>
       <c r="B130" t="inlineStr">
@@ -4447,14 +4447,14 @@
       </c>
       <c r="C130" t="inlineStr">
         <is>
-          <t>Additional Periodic Financial Information</t>
+          <t>Half Year Report</t>
         </is>
       </c>
     </row>
     <row r="131">
       <c r="A131" t="inlineStr">
         <is>
-          <t>GREEN OLEO S.p.A</t>
+          <t>VNE S.p.A.</t>
         </is>
       </c>
       <c r="B131" t="inlineStr">
@@ -4464,14 +4464,14 @@
       </c>
       <c r="C131" t="inlineStr">
         <is>
-          <t>Half Year Preliminary Results</t>
+          <t>Additional Periodic Financial Information</t>
         </is>
       </c>
     </row>
     <row r="132">
       <c r="A132" t="inlineStr">
         <is>
-          <t>CAIRO COMMUNICATION S.p.A.</t>
+          <t>Tinexta S.p.A.</t>
         </is>
       </c>
       <c r="B132" t="inlineStr">
@@ -4481,14 +4481,14 @@
       </c>
       <c r="C132" t="inlineStr">
         <is>
-          <t>Half Year Report</t>
+          <t>Analyst Presentation</t>
         </is>
       </c>
     </row>
     <row r="133">
       <c r="A133" t="inlineStr">
         <is>
-          <t>Comer Industries S.p.A.</t>
+          <t>Svas Biosana S.p.A.</t>
         </is>
       </c>
       <c r="B133" t="inlineStr">
@@ -4498,14 +4498,14 @@
       </c>
       <c r="C133" t="inlineStr">
         <is>
-          <t>Half Year Report</t>
+          <t>Half Year Preliminary Results</t>
         </is>
       </c>
     </row>
     <row r="134">
       <c r="A134" t="inlineStr">
         <is>
-          <t>BIESSE S.p.A.</t>
+          <t>Nusco S.p.A.</t>
         </is>
       </c>
       <c r="B134" t="inlineStr">
@@ -4515,14 +4515,14 @@
       </c>
       <c r="C134" t="inlineStr">
         <is>
-          <t>Half Year Report</t>
+          <t>Half Year Preliminary Results</t>
         </is>
       </c>
     </row>
     <row r="135">
       <c r="A135" t="inlineStr">
         <is>
-          <t>Basic Net S.p.A.</t>
+          <t>Comer Industries S.p.A.</t>
         </is>
       </c>
       <c r="B135" t="inlineStr">
@@ -4532,14 +4532,14 @@
       </c>
       <c r="C135" t="inlineStr">
         <is>
-          <t>Analyst Presentation</t>
+          <t>Half Year Report</t>
         </is>
       </c>
     </row>
     <row r="136">
       <c r="A136" t="inlineStr">
         <is>
-          <t>Basic Net S.p.A.</t>
+          <t>The Italian Sea Group S.p.A.</t>
         </is>
       </c>
       <c r="B136" t="inlineStr">
@@ -4549,14 +4549,14 @@
       </c>
       <c r="C136" t="inlineStr">
         <is>
-          <t>Half Year Report</t>
+          <t>Bod Annual Report</t>
         </is>
       </c>
     </row>
     <row r="137">
       <c r="A137" t="inlineStr">
         <is>
-          <t>EuroGroup Laminations S.p.A.</t>
+          <t>SALVATORE FERRAGAMO S.p.A.</t>
         </is>
       </c>
       <c r="B137" t="inlineStr">
@@ -4573,7 +4573,7 @@
     <row r="138">
       <c r="A138" t="inlineStr">
         <is>
-          <t>CLABO S.p.A.</t>
+          <t>SALVATORE FERRAGAMO S.p.A.</t>
         </is>
       </c>
       <c r="B138" t="inlineStr">
@@ -4583,14 +4583,14 @@
       </c>
       <c r="C138" t="inlineStr">
         <is>
-          <t>Additional Periodic Financial Information</t>
+          <t>Analyst Presentation</t>
         </is>
       </c>
     </row>
     <row r="139">
       <c r="A139" t="inlineStr">
         <is>
-          <t>Anima Holding S.p.A.</t>
+          <t>ENAV S.p.A.</t>
         </is>
       </c>
       <c r="B139" t="inlineStr">
@@ -4607,7 +4607,7 @@
     <row r="140">
       <c r="A140" t="inlineStr">
         <is>
-          <t>Alfonsino S.p.A.</t>
+          <t>CLABO S.p.A.</t>
         </is>
       </c>
       <c r="B140" t="inlineStr">
@@ -4617,14 +4617,14 @@
       </c>
       <c r="C140" t="inlineStr">
         <is>
-          <t>Half Year Report</t>
+          <t>Additional Periodic Financial Information</t>
         </is>
       </c>
     </row>
     <row r="141">
       <c r="A141" t="inlineStr">
         <is>
-          <t>ENAV S.p.A.</t>
+          <t>Anima Holding S.p.A.</t>
         </is>
       </c>
       <c r="B141" t="inlineStr">
@@ -4641,7 +4641,7 @@
     <row r="142">
       <c r="A142" t="inlineStr">
         <is>
-          <t>SALVATORE FERRAGAMO S.p.A.</t>
+          <t>Alfonsino S.p.A.</t>
         </is>
       </c>
       <c r="B142" t="inlineStr">
@@ -4658,7 +4658,7 @@
     <row r="143">
       <c r="A143" t="inlineStr">
         <is>
-          <t>SALVATORE FERRAGAMO S.p.A.</t>
+          <t>EuroGroup Laminations S.p.A.</t>
         </is>
       </c>
       <c r="B143" t="inlineStr">
@@ -4668,14 +4668,14 @@
       </c>
       <c r="C143" t="inlineStr">
         <is>
-          <t>Analyst Presentation</t>
+          <t>Half Year Report</t>
         </is>
       </c>
     </row>
     <row r="144">
       <c r="A144" t="inlineStr">
         <is>
-          <t>CAREL INDUSTRIES S.p.A.</t>
+          <t>INTERCOS S.p.A.</t>
         </is>
       </c>
       <c r="B144" t="inlineStr">
@@ -4685,14 +4685,14 @@
       </c>
       <c r="C144" t="inlineStr">
         <is>
-          <t>Half Year Report</t>
+          <t>Analyst Presentation</t>
         </is>
       </c>
     </row>
     <row r="145">
       <c r="A145" t="inlineStr">
         <is>
-          <t>CREDITO EMILIANO S.p.A.</t>
+          <t>WIIT S.p.A.</t>
         </is>
       </c>
       <c r="B145" t="inlineStr">
@@ -4709,7 +4709,7 @@
     <row r="146">
       <c r="A146" t="inlineStr">
         <is>
-          <t>DATALOGIC S.p.A.</t>
+          <t>WIIT S.p.A.</t>
         </is>
       </c>
       <c r="B146" t="inlineStr">
@@ -4719,14 +4719,14 @@
       </c>
       <c r="C146" t="inlineStr">
         <is>
-          <t>Half Year Report</t>
+          <t>Analyst Presentation</t>
         </is>
       </c>
     </row>
     <row r="147">
       <c r="A147" t="inlineStr">
         <is>
-          <t>IGD SIIQ S.p.A.</t>
+          <t>SAFILO GROUP S.p.A.</t>
         </is>
       </c>
       <c r="B147" t="inlineStr">
@@ -4760,7 +4760,7 @@
     <row r="149">
       <c r="A149" t="inlineStr">
         <is>
-          <t>INTERCOS S.p.A.</t>
+          <t>MARR S.p.A.</t>
         </is>
       </c>
       <c r="B149" t="inlineStr">
@@ -4770,14 +4770,14 @@
       </c>
       <c r="C149" t="inlineStr">
         <is>
-          <t>Analyst Presentation</t>
+          <t>Half Year Report</t>
         </is>
       </c>
     </row>
     <row r="150">
       <c r="A150" t="inlineStr">
         <is>
-          <t>MARR S.p.A.</t>
+          <t>INTERCOS S.p.A.</t>
         </is>
       </c>
       <c r="B150" t="inlineStr">
@@ -4794,7 +4794,7 @@
     <row r="151">
       <c r="A151" t="inlineStr">
         <is>
-          <t>SAFILO GROUP S.p.A.</t>
+          <t>BANCA IFIS S.p.A.</t>
         </is>
       </c>
       <c r="B151" t="inlineStr">
@@ -4804,14 +4804,14 @@
       </c>
       <c r="C151" t="inlineStr">
         <is>
-          <t>Half Year Report</t>
+          <t>Analyst Presentation</t>
         </is>
       </c>
     </row>
     <row r="152">
       <c r="A152" t="inlineStr">
         <is>
-          <t>WIIT S.p.A.</t>
+          <t>DATALOGIC S.p.A.</t>
         </is>
       </c>
       <c r="B152" t="inlineStr">
@@ -4828,7 +4828,7 @@
     <row r="153">
       <c r="A153" t="inlineStr">
         <is>
-          <t>INTERCOS S.p.A.</t>
+          <t>CREDITO EMILIANO S.p.A.</t>
         </is>
       </c>
       <c r="B153" t="inlineStr">
@@ -4845,7 +4845,7 @@
     <row r="154">
       <c r="A154" t="inlineStr">
         <is>
-          <t>BUZZI S.p.A.</t>
+          <t>CAREL INDUSTRIES S.p.A.</t>
         </is>
       </c>
       <c r="B154" t="inlineStr">
@@ -4862,7 +4862,7 @@
     <row r="155">
       <c r="A155" t="inlineStr">
         <is>
-          <t>WIIT S.p.A.</t>
+          <t>BUZZI S.p.A.</t>
         </is>
       </c>
       <c r="B155" t="inlineStr">
@@ -4872,7 +4872,7 @@
       </c>
       <c r="C155" t="inlineStr">
         <is>
-          <t>Analyst Presentation</t>
+          <t>Half Year Report</t>
         </is>
       </c>
     </row>
@@ -4896,7 +4896,7 @@
     <row r="157">
       <c r="A157" t="inlineStr">
         <is>
-          <t>BANCA IFIS S.p.A.</t>
+          <t>IGD SIIQ S.p.A.</t>
         </is>
       </c>
       <c r="B157" t="inlineStr">
@@ -4906,14 +4906,14 @@
       </c>
       <c r="C157" t="inlineStr">
         <is>
-          <t>Analyst Presentation</t>
+          <t>Half Year Report</t>
         </is>
       </c>
     </row>
     <row r="158">
       <c r="A158" t="inlineStr">
         <is>
-          <t>TESMEC S.p.A.</t>
+          <t>doValue S.p.A.</t>
         </is>
       </c>
       <c r="B158" t="inlineStr">
@@ -4930,7 +4930,7 @@
     <row r="159">
       <c r="A159" t="inlineStr">
         <is>
-          <t>SIT S.p.A.</t>
+          <t>Technoprobe S.p.A.</t>
         </is>
       </c>
       <c r="B159" t="inlineStr">
@@ -4940,14 +4940,14 @@
       </c>
       <c r="C159" t="inlineStr">
         <is>
-          <t>Analyst Presentation</t>
+          <t>Half Year Report</t>
         </is>
       </c>
     </row>
     <row r="160">
       <c r="A160" t="inlineStr">
         <is>
-          <t>SIT S.p.A.</t>
+          <t>TREVI - Finanziaria Industriale S.p.A.</t>
         </is>
       </c>
       <c r="B160" t="inlineStr">
@@ -4964,7 +4964,7 @@
     <row r="161">
       <c r="A161" t="inlineStr">
         <is>
-          <t>RISANAMENTO S.p.A.</t>
+          <t>TESMEC S.p.A.</t>
         </is>
       </c>
       <c r="B161" t="inlineStr">
@@ -4974,14 +4974,14 @@
       </c>
       <c r="C161" t="inlineStr">
         <is>
-          <t>Bod Annual Report</t>
+          <t>Analyst Presentation</t>
         </is>
       </c>
     </row>
     <row r="162">
       <c r="A162" t="inlineStr">
         <is>
-          <t>RISANAMENTO S.p.A.</t>
+          <t>TESMEC S.p.A.</t>
         </is>
       </c>
       <c r="B162" t="inlineStr">
@@ -4998,7 +4998,7 @@
     <row r="163">
       <c r="A163" t="inlineStr">
         <is>
-          <t>PIQUADRO S.p.A.</t>
+          <t>SIT S.p.A.</t>
         </is>
       </c>
       <c r="B163" t="inlineStr">
@@ -5008,14 +5008,14 @@
       </c>
       <c r="C163" t="inlineStr">
         <is>
-          <t>Additional Periodic Financial Information</t>
+          <t>Analyst Presentation</t>
         </is>
       </c>
     </row>
     <row r="164">
       <c r="A164" t="inlineStr">
         <is>
-          <t>OSAI Automation System S.p.A.</t>
+          <t>SIT S.p.A.</t>
         </is>
       </c>
       <c r="B164" t="inlineStr">
@@ -5025,14 +5025,14 @@
       </c>
       <c r="C164" t="inlineStr">
         <is>
-          <t>Bod Annual Report</t>
+          <t>Half Year Report</t>
         </is>
       </c>
     </row>
     <row r="165">
       <c r="A165" t="inlineStr">
         <is>
-          <t>OSAI Automation System S.p.A.</t>
+          <t>RISANAMENTO S.p.A.</t>
         </is>
       </c>
       <c r="B165" t="inlineStr">
@@ -5042,14 +5042,14 @@
       </c>
       <c r="C165" t="inlineStr">
         <is>
-          <t>Half Year Report</t>
+          <t>Bod Annual Report</t>
         </is>
       </c>
     </row>
     <row r="166">
       <c r="A166" t="inlineStr">
         <is>
-          <t>Neodecortech S.p.A.</t>
+          <t>RISANAMENTO S.p.A.</t>
         </is>
       </c>
       <c r="B166" t="inlineStr">
@@ -5059,14 +5059,14 @@
       </c>
       <c r="C166" t="inlineStr">
         <is>
-          <t>Half Year Report</t>
+          <t>Additional Periodic Financial Information</t>
         </is>
       </c>
     </row>
     <row r="167">
       <c r="A167" t="inlineStr">
         <is>
-          <t>Masi Agricola S.p.A.</t>
+          <t>Technoprobe S.p.A.</t>
         </is>
       </c>
       <c r="B167" t="inlineStr">
@@ -5076,14 +5076,14 @@
       </c>
       <c r="C167" t="inlineStr">
         <is>
-          <t>Half Year Report</t>
+          <t>Analyst Presentation</t>
         </is>
       </c>
     </row>
     <row r="168">
       <c r="A168" t="inlineStr">
         <is>
-          <t>INTERPUMP GROUP S.p.A.</t>
+          <t>PIQUADRO S.p.A.</t>
         </is>
       </c>
       <c r="B168" t="inlineStr">
@@ -5093,14 +5093,14 @@
       </c>
       <c r="C168" t="inlineStr">
         <is>
-          <t>Half Year Report</t>
+          <t>Additional Periodic Financial Information</t>
         </is>
       </c>
     </row>
     <row r="169">
       <c r="A169" t="inlineStr">
         <is>
-          <t>Bper Banca S.P.A.</t>
+          <t>RISANAMENTO S.p.A.</t>
         </is>
       </c>
       <c r="B169" t="inlineStr">
@@ -5117,7 +5117,7 @@
     <row r="170">
       <c r="A170" t="inlineStr">
         <is>
-          <t>RISANAMENTO S.p.A.</t>
+          <t>Banco BPM S.p.A.</t>
         </is>
       </c>
       <c r="B170" t="inlineStr">
@@ -5127,14 +5127,14 @@
       </c>
       <c r="C170" t="inlineStr">
         <is>
-          <t>Additional Periodic Financial Information</t>
+          <t>Half Year Report</t>
         </is>
       </c>
     </row>
     <row r="171">
       <c r="A171" t="inlineStr">
         <is>
-          <t>BFF Bank S.P.A.</t>
+          <t>Bper Banca S.P.A.</t>
         </is>
       </c>
       <c r="B171" t="inlineStr">
@@ -5151,7 +5151,7 @@
     <row r="172">
       <c r="A172" t="inlineStr">
         <is>
-          <t>doValue S.p.A.</t>
+          <t>INTERPUMP GROUP S.p.A.</t>
         </is>
       </c>
       <c r="B172" t="inlineStr">
@@ -5168,7 +5168,7 @@
     <row r="173">
       <c r="A173" t="inlineStr">
         <is>
-          <t>Technoprobe S.p.A.</t>
+          <t>BFF Bank S.P.A.</t>
         </is>
       </c>
       <c r="B173" t="inlineStr">
@@ -5178,14 +5178,14 @@
       </c>
       <c r="C173" t="inlineStr">
         <is>
-          <t>Analyst Presentation</t>
+          <t>Half Year Report</t>
         </is>
       </c>
     </row>
     <row r="174">
       <c r="A174" t="inlineStr">
         <is>
-          <t>Technoprobe S.p.A.</t>
+          <t>Neodecortech S.p.A.</t>
         </is>
       </c>
       <c r="B174" t="inlineStr">
@@ -5202,7 +5202,7 @@
     <row r="175">
       <c r="A175" t="inlineStr">
         <is>
-          <t>TREVI - Finanziaria Industriale S.p.A.</t>
+          <t>OSAI Automation System S.p.A.</t>
         </is>
       </c>
       <c r="B175" t="inlineStr">
@@ -5219,7 +5219,7 @@
     <row r="176">
       <c r="A176" t="inlineStr">
         <is>
-          <t>TESMEC S.p.A.</t>
+          <t>OSAI Automation System S.p.A.</t>
         </is>
       </c>
       <c r="B176" t="inlineStr">
@@ -5229,14 +5229,14 @@
       </c>
       <c r="C176" t="inlineStr">
         <is>
-          <t>Analyst Presentation</t>
+          <t>Bod Annual Report</t>
         </is>
       </c>
     </row>
     <row r="177">
       <c r="A177" t="inlineStr">
         <is>
-          <t>Banco BPM S.p.A.</t>
+          <t>Masi Agricola S.p.A.</t>
         </is>
       </c>
       <c r="B177" t="inlineStr">
@@ -5253,7 +5253,7 @@
     <row r="178">
       <c r="A178" t="inlineStr">
         <is>
-          <t>F.I.L.A. S.p.A.</t>
+          <t>Mediobanca Banca di Credito Finanziario S.p.A.</t>
         </is>
       </c>
       <c r="B178" t="inlineStr">
@@ -5270,7 +5270,7 @@
     <row r="179">
       <c r="A179" t="inlineStr">
         <is>
-          <t>GEFRAN S.p.A.</t>
+          <t>ITALIAN EXHIBITION GROUP S.p.A.</t>
         </is>
       </c>
       <c r="B179" t="inlineStr">
@@ -5304,7 +5304,7 @@
     <row r="181">
       <c r="A181" t="inlineStr">
         <is>
-          <t>ITALIAN EXHIBITION GROUP S.p.A.</t>
+          <t>GEFRAN S.p.A.</t>
         </is>
       </c>
       <c r="B181" t="inlineStr">
@@ -5321,7 +5321,7 @@
     <row r="182">
       <c r="A182" t="inlineStr">
         <is>
-          <t>Mediobanca Banca di Credito Finanziario S.p.A.</t>
+          <t>F.I.L.A. S.p.A.</t>
         </is>
       </c>
       <c r="B182" t="inlineStr">
@@ -5338,7 +5338,7 @@
     <row r="183">
       <c r="A183" t="inlineStr">
         <is>
-          <t>Neodecortech S.p.A.</t>
+          <t>Bper Banca S.P.A.</t>
         </is>
       </c>
       <c r="B183" t="inlineStr">
@@ -5355,7 +5355,7 @@
     <row r="184">
       <c r="A184" t="inlineStr">
         <is>
-          <t>OPS Retail S.p.A.</t>
+          <t>Banca Monte dei Paschi di Siena S.p.A.</t>
         </is>
       </c>
       <c r="B184" t="inlineStr">
@@ -5365,14 +5365,14 @@
       </c>
       <c r="C184" t="inlineStr">
         <is>
-          <t>Bod Annual Report</t>
+          <t>Half Year Report</t>
         </is>
       </c>
     </row>
     <row r="185">
       <c r="A185" t="inlineStr">
         <is>
-          <t>Unipol S.p.A.</t>
+          <t>BANCA SISTEMA S.p.A.</t>
         </is>
       </c>
       <c r="B185" t="inlineStr">
@@ -5389,7 +5389,7 @@
     <row r="186">
       <c r="A186" t="inlineStr">
         <is>
-          <t>REVO Insurance S.p.A.</t>
+          <t>TXT E-SOLUTIONS S.p.A.</t>
         </is>
       </c>
       <c r="B186" t="inlineStr">
@@ -5406,7 +5406,7 @@
     <row r="187">
       <c r="A187" t="inlineStr">
         <is>
-          <t>PROMOTICA S.p.A.</t>
+          <t>Unipol S.p.A.</t>
         </is>
       </c>
       <c r="B187" t="inlineStr">
@@ -5416,14 +5416,14 @@
       </c>
       <c r="C187" t="inlineStr">
         <is>
-          <t>Half Year Preliminary Results</t>
+          <t>Half Year Report</t>
         </is>
       </c>
     </row>
     <row r="188">
       <c r="A188" t="inlineStr">
         <is>
-          <t>ASSICURAZIONI GENERALI S.p.A.</t>
+          <t>REVO Insurance S.p.A.</t>
         </is>
       </c>
       <c r="B188" t="inlineStr">
@@ -5433,14 +5433,14 @@
       </c>
       <c r="C188" t="inlineStr">
         <is>
-          <t>Analyst Presentation</t>
+          <t>Half Year Report</t>
         </is>
       </c>
     </row>
     <row r="189">
       <c r="A189" t="inlineStr">
         <is>
-          <t>ASSICURAZIONI GENERALI S.p.A.</t>
+          <t>PROMOTICA S.p.A.</t>
         </is>
       </c>
       <c r="B189" t="inlineStr">
@@ -5450,14 +5450,14 @@
       </c>
       <c r="C189" t="inlineStr">
         <is>
-          <t>Half Year Report</t>
+          <t>Half Year Preliminary Results</t>
         </is>
       </c>
     </row>
     <row r="190">
       <c r="A190" t="inlineStr">
         <is>
-          <t>Abitare In S.p.A.</t>
+          <t>BANCA SISTEMA S.p.A.</t>
         </is>
       </c>
       <c r="B190" t="inlineStr">
@@ -5467,14 +5467,14 @@
       </c>
       <c r="C190" t="inlineStr">
         <is>
-          <t>Additional Periodic Financial Information</t>
+          <t>Analyst Presentation</t>
         </is>
       </c>
     </row>
     <row r="191">
       <c r="A191" t="inlineStr">
         <is>
-          <t>BANCA SISTEMA S.p.A.</t>
+          <t>Abitare In S.p.A.</t>
         </is>
       </c>
       <c r="B191" t="inlineStr">
@@ -5484,14 +5484,14 @@
       </c>
       <c r="C191" t="inlineStr">
         <is>
-          <t>Analyst Presentation</t>
+          <t>Additional Periodic Financial Information</t>
         </is>
       </c>
     </row>
     <row r="192">
       <c r="A192" t="inlineStr">
         <is>
-          <t>BANCA SISTEMA S.p.A.</t>
+          <t>ASSICURAZIONI GENERALI S.p.A.</t>
         </is>
       </c>
       <c r="B192" t="inlineStr">
@@ -5508,7 +5508,7 @@
     <row r="193">
       <c r="A193" t="inlineStr">
         <is>
-          <t>Banca Monte dei Paschi di Siena S.p.A.</t>
+          <t>ASSICURAZIONI GENERALI S.p.A.</t>
         </is>
       </c>
       <c r="B193" t="inlineStr">
@@ -5518,14 +5518,14 @@
       </c>
       <c r="C193" t="inlineStr">
         <is>
-          <t>Half Year Report</t>
+          <t>Analyst Presentation</t>
         </is>
       </c>
     </row>
     <row r="194">
       <c r="A194" t="inlineStr">
         <is>
-          <t>TXT E-SOLUTIONS S.p.A.</t>
+          <t>Neodecortech S.p.A.</t>
         </is>
       </c>
       <c r="B194" t="inlineStr">
@@ -5535,14 +5535,14 @@
       </c>
       <c r="C194" t="inlineStr">
         <is>
-          <t>Half Year Report</t>
+          <t>Analyst Presentation</t>
         </is>
       </c>
     </row>
     <row r="195">
       <c r="A195" t="inlineStr">
         <is>
-          <t>Bper Banca S.P.A.</t>
+          <t>OPS Retail S.p.A.</t>
         </is>
       </c>
       <c r="B195" t="inlineStr">
@@ -5552,14 +5552,14 @@
       </c>
       <c r="C195" t="inlineStr">
         <is>
-          <t>Analyst Presentation</t>
+          <t>Bod Annual Report</t>
         </is>
       </c>
     </row>
     <row r="196">
       <c r="A196" t="inlineStr">
         <is>
-          <t>EMAK S.p.A.</t>
+          <t>Iniziative Bresciane - INBRE - S.p.A.</t>
         </is>
       </c>
       <c r="B196" t="inlineStr">
@@ -5576,7 +5576,7 @@
     <row r="197">
       <c r="A197" t="inlineStr">
         <is>
-          <t>Iniziative Bresciane - INBRE - S.p.A.</t>
+          <t>Riba Mundo Tecnologia S.A.</t>
         </is>
       </c>
       <c r="B197" t="inlineStr">
@@ -5586,14 +5586,14 @@
       </c>
       <c r="C197" t="inlineStr">
         <is>
-          <t>Half Year Report</t>
+          <t>Half Year Preliminary Results</t>
         </is>
       </c>
     </row>
     <row r="198">
       <c r="A198" t="inlineStr">
         <is>
-          <t>Riba Mundo Tecnologia S.A.</t>
+          <t>Unipol S.p.A.</t>
         </is>
       </c>
       <c r="B198" t="inlineStr">
@@ -5603,14 +5603,14 @@
       </c>
       <c r="C198" t="inlineStr">
         <is>
-          <t>Half Year Preliminary Results</t>
+          <t>Analyst Presentation</t>
         </is>
       </c>
     </row>
     <row r="199">
       <c r="A199" t="inlineStr">
         <is>
-          <t>Unipol S.p.A.</t>
+          <t>EMAK S.p.A.</t>
         </is>
       </c>
       <c r="B199" t="inlineStr">
@@ -5620,7 +5620,7 @@
       </c>
       <c r="C199" t="inlineStr">
         <is>
-          <t>Analyst Presentation</t>
+          <t>Half Year Report</t>
         </is>
       </c>
     </row>
